--- a/Excelファイル/結婚式用文章席札.xlsx
+++ b/Excelファイル/結婚式用文章席札.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlpe\Downloads\Desktop\GitHub\hsks-wedding-site1994\Excelファイル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BA0414-9120-46AE-B57D-D3E239D17757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7005E1A0-EA10-41D5-8C3F-326B4CCE80A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="240" windowWidth="19360" windowHeight="10480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
   <si>
     <t>区分</t>
   </si>
@@ -352,13 +352,7 @@
 明るくていつもその場を楽しく盛り上げてくれるえっちゃんが大好きです。これからも夫婦共々お世話になります。これからもよろしくね！！</t>
   </si>
   <si>
-    <t>桑原愛</t>
-  </si>
-  <si>
     <t>ながおか</t>
-  </si>
-  <si>
-    <t>安達哲浩</t>
   </si>
   <si>
     <t>大平里美</t>
@@ -1017,7 +1011,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="4" max="4" width="7.83203125" style="4" bestFit="1" customWidth="1"/>
@@ -1834,13 +1828,17 @@
         <v>55</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -1871,13 +1869,17 @@
         <v>55</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -1908,16 +1910,16 @@
         <v>55</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1949,16 +1951,16 @@
         <v>55</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -1990,16 +1992,16 @@
         <v>55</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -2031,16 +2033,16 @@
         <v>55</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -2072,16 +2074,16 @@
         <v>55</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -2113,16 +2115,16 @@
         <v>55</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -2149,88 +2151,6 @@
       <c r="AB37" s="2"/>
       <c r="AC37" s="2"/>
     </row>
-    <row r="38" spans="1:29" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>55</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
-      <c r="P38" s="2"/>
-      <c r="Q38" s="2"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="2"/>
-      <c r="T38" s="2"/>
-      <c r="U38" s="2"/>
-      <c r="V38" s="2"/>
-      <c r="W38" s="2"/>
-      <c r="X38" s="2"/>
-      <c r="Y38" s="2"/>
-      <c r="Z38" s="2"/>
-      <c r="AA38" s="2"/>
-      <c r="AB38" s="2"/>
-      <c r="AC38" s="2"/>
-    </row>
-    <row r="39" spans="1:29" ht="18.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
-      <c r="P39" s="2"/>
-      <c r="Q39" s="2"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="2"/>
-      <c r="T39" s="2"/>
-      <c r="U39" s="2"/>
-      <c r="V39" s="2"/>
-      <c r="W39" s="2"/>
-      <c r="X39" s="2"/>
-      <c r="Y39" s="2"/>
-      <c r="Z39" s="2"/>
-      <c r="AA39" s="2"/>
-      <c r="AB39" s="2"/>
-      <c r="AC39" s="2"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2251,102 +2171,102 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>131</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>133</v>
       </c>
       <c r="E2" s="6"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>135</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>145</v>
       </c>
       <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>147</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>56</v>
@@ -2355,63 +2275,63 @@
         <v>56</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>155</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>72</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>163</v>
-      </c>
       <c r="E10" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Excelファイル/結婚式用文章席札.xlsx
+++ b/Excelファイル/結婚式用文章席札.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\orlpe\Downloads\Desktop\GitHub\hsks-wedding-site1994\Excelファイル\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7005E1A0-EA10-41D5-8C3F-326B4CCE80A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4EEC4C-4C07-44F0-8A51-D4A011951F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="164">
   <si>
     <t>区分</t>
   </si>
@@ -567,12 +567,16 @@
   <si>
     <t>※ Sheet1には「みつけ」「ながおか」グループの名簿もありますが、guests.js側に合言葉が未設定のため未掲載です。</t>
   </si>
+  <si>
+    <t>みつけ</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -612,6 +616,13 @@
       <sz val="10"/>
       <color rgb="FF808080"/>
       <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -673,7 +684,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -697,6 +708,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1704,8 +1718,8 @@
       <c r="A27" t="s">
         <v>55</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>88</v>
+      <c r="B27" s="9" t="s">
+        <v>163</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>89</v>
@@ -2154,7 +2168,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
